--- a/public/downloads/TangModeling2020.xlsx
+++ b/public/downloads/TangModeling2020.xlsx
@@ -8,27 +8,29 @@
   </bookViews>
   <sheets>
     <sheet name="MLIP_Data" sheetId="1" r:id="rId1"/>
-    <sheet name="anomaly" sheetId="2" r:id="rId2"/>
-    <sheet name="AlphaNet-v1-OMA" sheetId="3" r:id="rId3"/>
-    <sheet name="CHGNetv0.3.0" sheetId="4" r:id="rId4"/>
-    <sheet name="DPA-3.1-3M-FT" sheetId="5" r:id="rId5"/>
-    <sheet name="Eqnorm-MPtrj" sheetId="6" r:id="rId6"/>
-    <sheet name="eSEN-30M-OAM" sheetId="7" r:id="rId7"/>
-    <sheet name="GRACE-2L-OAM" sheetId="8" r:id="rId8"/>
-    <sheet name="MACE-MPA-0" sheetId="9" r:id="rId9"/>
-    <sheet name="MATLANTISv8" sheetId="10" r:id="rId10"/>
-    <sheet name="MatterSim_v1_5M" sheetId="11" r:id="rId11"/>
-    <sheet name="ORB-v3" sheetId="12" r:id="rId12"/>
-    <sheet name="SevenNet-MF-OMPA" sheetId="13" r:id="rId13"/>
-    <sheet name="UMA-m-1p1_oc20" sheetId="14" r:id="rId14"/>
-    <sheet name="UMA-s-1p1_oc20" sheetId="15" r:id="rId15"/>
+    <sheet name="MLIP_Data_shifted" sheetId="2" r:id="rId2"/>
+    <sheet name="anomaly" sheetId="3" r:id="rId3"/>
+    <sheet name="anomaly_shifted" sheetId="4" r:id="rId4"/>
+    <sheet name="AlphaNet-v1-OMA" sheetId="5" r:id="rId5"/>
+    <sheet name="CHGNetv0.3.0" sheetId="6" r:id="rId6"/>
+    <sheet name="DPA-3.1-3M-FT" sheetId="7" r:id="rId7"/>
+    <sheet name="Eqnorm-MPtrj" sheetId="8" r:id="rId8"/>
+    <sheet name="eSEN-30M-OAM" sheetId="9" r:id="rId9"/>
+    <sheet name="GRACE-2L-OAM" sheetId="10" r:id="rId10"/>
+    <sheet name="MACE-MPA-0" sheetId="11" r:id="rId11"/>
+    <sheet name="MATLANTISv8" sheetId="12" r:id="rId12"/>
+    <sheet name="MatterSim_v1_5M" sheetId="13" r:id="rId13"/>
+    <sheet name="ORB-v3" sheetId="14" r:id="rId14"/>
+    <sheet name="SevenNet-MF-OMPA" sheetId="15" r:id="rId15"/>
+    <sheet name="UMA-m-1p1_oc20" sheetId="16" r:id="rId16"/>
+    <sheet name="UMA-s-1p1_oc20" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="51">
   <si>
     <t>MLIP_name</t>
   </si>
@@ -60,10 +62,10 @@
     <t>Num_total</t>
   </si>
   <si>
-    <t>Time_total (s)</t>
+    <t>Time_total (ms)</t>
   </si>
   <si>
-    <t>Time_per_step (s)</t>
+    <t>Time_per_step (ms)</t>
   </si>
   <si>
     <t>Steps_total</t>
@@ -157,6 +159,27 @@
   </si>
   <si>
     <t>Adsorbate_name</t>
+  </si>
+  <si>
+    <t>Gas shift correction</t>
+  </si>
+  <si>
+    <t>Shift (eV)</t>
+  </si>
+  <si>
+    <t>N_fit</t>
+  </si>
+  <si>
+    <t>MAE_total_shifted (eV)</t>
+  </si>
+  <si>
+    <t>MAE_normal_shifted (eV)</t>
+  </si>
+  <si>
+    <t>Num_normal_shifted</t>
+  </si>
+  <si>
+    <t>Num_energy_anomaly_shifted</t>
   </si>
   <si>
     <t>H</t>
@@ -645,10 +668,10 @@
         <v>65</v>
       </c>
       <c r="N3" s="5">
-        <v>146.9144349098206</v>
+        <v>146914.4349098206</v>
       </c>
       <c r="O3" s="4">
-        <v>0.03174469207213063</v>
+        <v>31.74469207213063</v>
       </c>
       <c r="P3" s="5">
         <v>4628</v>
@@ -695,10 +718,10 @@
         <v>65</v>
       </c>
       <c r="N4" s="5">
-        <v>688.9376592636108</v>
+        <v>688937.6592636108</v>
       </c>
       <c r="O4" s="4">
-        <v>0.0571590192701909</v>
+        <v>57.1590192701909</v>
       </c>
       <c r="P4" s="5">
         <v>12053</v>
@@ -745,10 +768,10 @@
         <v>65</v>
       </c>
       <c r="N5" s="5">
-        <v>686.2098686695099</v>
+        <v>686209.8686695099</v>
       </c>
       <c r="O5" s="4">
-        <v>0.158844877006831</v>
+        <v>158.844877006831</v>
       </c>
       <c r="P5" s="5">
         <v>4320</v>
@@ -795,10 +818,10 @@
         <v>65</v>
       </c>
       <c r="N6" s="5">
-        <v>580.2850821018219</v>
+        <v>580285.0821018219</v>
       </c>
       <c r="O6" s="4">
-        <v>0.08536114770547541</v>
+        <v>85.36114770547542</v>
       </c>
       <c r="P6" s="5">
         <v>6798</v>
@@ -845,10 +868,10 @@
         <v>65</v>
       </c>
       <c r="N7" s="5">
-        <v>878.0030016899109</v>
+        <v>878003.0016899109</v>
       </c>
       <c r="O7" s="4">
-        <v>0.219226717026195</v>
+        <v>219.226717026195</v>
       </c>
       <c r="P7" s="5">
         <v>4005</v>
@@ -895,10 +918,10 @@
         <v>65</v>
       </c>
       <c r="N8" s="5">
-        <v>65.10309767723083</v>
+        <v>65103.09767723083</v>
       </c>
       <c r="O8" s="4">
-        <v>0.01544557477514373</v>
+        <v>15.44557477514373</v>
       </c>
       <c r="P8" s="5">
         <v>4215</v>
@@ -945,10 +968,10 @@
         <v>65</v>
       </c>
       <c r="N9" s="5">
-        <v>245.0429632663727</v>
+        <v>245042.9632663727</v>
       </c>
       <c r="O9" s="4">
-        <v>0.02920655104485968</v>
+        <v>29.20655104485968</v>
       </c>
       <c r="P9" s="5">
         <v>8390</v>
@@ -995,10 +1018,10 @@
         <v>65</v>
       </c>
       <c r="N10" s="5">
-        <v>363.6943655014038</v>
+        <v>363694.3655014038</v>
       </c>
       <c r="O10" s="4">
-        <v>0.08292165196110438</v>
+        <v>82.92165196110437</v>
       </c>
       <c r="P10" s="5">
         <v>4386</v>
@@ -1045,10 +1068,10 @@
         <v>65</v>
       </c>
       <c r="N11" s="5">
-        <v>173.7538969516754</v>
+        <v>173753.8969516754</v>
       </c>
       <c r="O11" s="4">
-        <v>0.03953444754304333</v>
+        <v>39.53444754304333</v>
       </c>
       <c r="P11" s="5">
         <v>4395</v>
@@ -1095,10 +1118,10 @@
         <v>65</v>
       </c>
       <c r="N12" s="5">
-        <v>91.54558324813843</v>
+        <v>91545.58324813843</v>
       </c>
       <c r="O12" s="4">
-        <v>0.01990554104112599</v>
+        <v>19.90554104112599</v>
       </c>
       <c r="P12" s="5">
         <v>4599</v>
@@ -1145,10 +1168,10 @@
         <v>65</v>
       </c>
       <c r="N13" s="5">
-        <v>296.9700620174408</v>
+        <v>296970.0620174408</v>
       </c>
       <c r="O13" s="4">
-        <v>0.07414982821908635</v>
+        <v>74.14982821908634</v>
       </c>
       <c r="P13" s="5">
         <v>4005</v>
@@ -1195,10 +1218,10 @@
         <v>65</v>
       </c>
       <c r="N14" s="5">
-        <v>1064.915188789368</v>
+        <v>1064915.188789368</v>
       </c>
       <c r="O14" s="4">
-        <v>0.3380683139013866</v>
+        <v>338.0683139013866</v>
       </c>
       <c r="P14" s="5">
         <v>3150</v>
@@ -1245,10 +1268,10 @@
         <v>50</v>
       </c>
       <c r="N15" s="5">
-        <v>191.1869747638702</v>
+        <v>191186.9747638702</v>
       </c>
       <c r="O15" s="4">
-        <v>0.09764401162608286</v>
+        <v>97.64401162608286</v>
       </c>
       <c r="P15" s="5">
         <v>1958</v>
@@ -1276,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1287,9 +1310,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1323,8 +1352,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1346,50 +1383,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
-        <v>0.2320150863698463</v>
+        <v>0.3185467934058848</v>
       </c>
       <c r="C3" s="4">
-        <v>0.1916190924673678</v>
+        <v>0.285872539110592</v>
       </c>
       <c r="D3" s="4">
-        <v>0.1912560134856861</v>
+        <v>0.2824052655040622</v>
       </c>
       <c r="E3" s="4">
-        <v>83.51334379905812</v>
+        <v>86.00313971742565</v>
       </c>
       <c r="F3" s="4">
-        <v>90.1302701772471</v>
+        <v>89.93288590604195</v>
       </c>
       <c r="G3" s="5">
         <v>65</v>
       </c>
       <c r="H3" s="5">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.285872539110592</v>
+      </c>
+      <c r="O3" s="5">
+        <v>61</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09713489805975625</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.06832074294549072</v>
+      </c>
+      <c r="R3" s="5">
+        <v>61</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1400,6 +1473,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1407,7 +1481,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1418,9 +1492,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1454,8 +1534,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1477,50 +1565,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3004123511005533</v>
+        <v>0.4458304534395351</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3004123511005533</v>
+        <v>0.3637836354814282</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2895910893278107</v>
+        <v>0.3383042683554007</v>
       </c>
       <c r="E3" s="4">
-        <v>83.76452119309262</v>
+        <v>80.10465724751438</v>
       </c>
       <c r="F3" s="4">
-        <v>89.79401135776982</v>
+        <v>81.88280846669913</v>
       </c>
       <c r="G3" s="5">
         <v>65</v>
       </c>
       <c r="H3" s="5">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.3573543718682087</v>
+      </c>
+      <c r="O3" s="5">
+        <v>57</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2559610977691249</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1598046990807221</v>
+      </c>
+      <c r="R3" s="5">
+        <v>57</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1531,6 +1655,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1538,7 +1663,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1549,9 +1674,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1585,8 +1716,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1608,25 +1747,43 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
-        <v>0.3190046188569305</v>
+        <v>0.2320150863698463</v>
       </c>
       <c r="C3" s="4">
-        <v>0.2897454035183828</v>
+        <v>0.1916190924673678</v>
       </c>
       <c r="D3" s="4">
-        <v>0.2905641877567037</v>
+        <v>0.1912560134856861</v>
       </c>
       <c r="E3" s="4">
-        <v>80.27734170591329</v>
+        <v>83.51334379905812</v>
       </c>
       <c r="F3" s="4">
-        <v>88.12183789364718</v>
+        <v>90.1302701772471</v>
       </c>
       <c r="G3" s="5">
         <v>65</v>
@@ -1649,9 +1806,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1893666925516583</v>
+      </c>
+      <c r="O3" s="5">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09852245375034556</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05388859849486697</v>
+      </c>
+      <c r="R3" s="5">
+        <v>63</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1662,6 +1837,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1669,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1680,9 +1856,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1716,8 +1898,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1739,50 +1929,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
-        <v>0.4772725790385336</v>
+        <v>0.3004123511005533</v>
       </c>
       <c r="C3" s="4">
-        <v>0.4588009637968969</v>
+        <v>0.3004123511005533</v>
       </c>
       <c r="D3" s="4">
-        <v>0.4542283746745223</v>
+        <v>0.2895910893278107</v>
       </c>
       <c r="E3" s="4">
-        <v>85.81004709576142</v>
+        <v>83.76452119309262</v>
       </c>
       <c r="F3" s="4">
-        <v>90.65943899500645</v>
+        <v>89.79401135776982</v>
       </c>
       <c r="G3" s="5">
         <v>65</v>
       </c>
       <c r="H3" s="5">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2975776994144186</v>
+      </c>
+      <c r="O3" s="5">
+        <v>65</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1172116872151975</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.1172116872151975</v>
+      </c>
+      <c r="R3" s="5">
+        <v>65</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1793,6 +2019,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1800,7 +2027,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1811,9 +2038,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1847,8 +2080,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1870,50 +2111,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
-        <v>0.08938248716024445</v>
+        <v>0.3190046188569305</v>
       </c>
       <c r="C3" s="4">
-        <v>0.08938248716024445</v>
+        <v>0.2897454035183828</v>
       </c>
       <c r="D3" s="4">
-        <v>0.09032717493022666</v>
+        <v>0.2905641877567037</v>
       </c>
       <c r="E3" s="4">
-        <v>97.06855049712192</v>
+        <v>80.27734170591329</v>
       </c>
       <c r="F3" s="4">
-        <v>98.26587506453281</v>
+        <v>88.12183789364718</v>
       </c>
       <c r="G3" s="5">
         <v>65</v>
       </c>
       <c r="H3" s="5">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
         <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2897454035183828</v>
+      </c>
+      <c r="O3" s="5">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.09310003361223429</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05666924413893436</v>
+      </c>
+      <c r="R3" s="5">
+        <v>63</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -1924,6 +2201,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1931,7 +2209,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1942,9 +2220,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -1978,8 +2262,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2001,50 +2293,86 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
-        <v>0.09755729918485159</v>
+        <v>0.4772725790385336</v>
       </c>
       <c r="C3" s="4">
-        <v>0.0976706311271209</v>
+        <v>0.4588009637968969</v>
       </c>
       <c r="D3" s="4">
-        <v>0.0979023293138097</v>
+        <v>0.4542283746745223</v>
       </c>
       <c r="E3" s="4">
-        <v>96.16462585034012</v>
+        <v>85.81004709576142</v>
       </c>
       <c r="F3" s="4">
-        <v>97.16689038031402</v>
+        <v>90.65943899500645</v>
       </c>
       <c r="G3" s="5">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="H3" s="5">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
       </c>
       <c r="J3" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.4588009637968969</v>
+      </c>
+      <c r="O3" s="5">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08368037793992791</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05271377218722443</v>
+      </c>
+      <c r="R3" s="5">
+        <v>63</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2055,12 +2383,1134 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.08938248716024445</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.08938248716024445</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.09032717493022666</v>
+      </c>
+      <c r="E3" s="4">
+        <v>97.06855049712192</v>
+      </c>
+      <c r="F3" s="4">
+        <v>98.26587506453281</v>
+      </c>
+      <c r="G3" s="5">
+        <v>65</v>
+      </c>
+      <c r="H3" s="5">
+        <v>65</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.08938248716024445</v>
+      </c>
+      <c r="O3" s="5">
+        <v>65</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.02777887195116797</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.02777887195116797</v>
+      </c>
+      <c r="R3" s="5">
+        <v>65</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="4" width="18.7109375" customWidth="1"/>
+    <col min="5" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="25.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.09755729918485159</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.0976706311271209</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.0979023293138097</v>
+      </c>
+      <c r="E3" s="4">
+        <v>96.16462585034012</v>
+      </c>
+      <c r="F3" s="4">
+        <v>97.16689038031402</v>
+      </c>
+      <c r="G3" s="5">
+        <v>50</v>
+      </c>
+      <c r="H3" s="5">
+        <v>49</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>-0.0976706311271209</v>
+      </c>
+      <c r="O3" s="5">
+        <v>49</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.03554854357360267</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.03615837921564628</v>
+      </c>
+      <c r="R3" s="5">
+        <v>49</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>89.23076923076924</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="D3" s="3">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>9.230769230769232</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.1007170015231462</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0.05897705439066708</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0.06088286313725737</v>
+      </c>
+      <c r="K3" s="4">
+        <v>85.24803767660921</v>
+      </c>
+      <c r="L3" s="4">
+        <v>88.93787644122902</v>
+      </c>
+      <c r="M3" s="5">
+        <v>65</v>
+      </c>
+      <c r="N3" s="5">
+        <v>146914.4349098206</v>
+      </c>
+      <c r="O3" s="4">
+        <v>31.74469207213063</v>
+      </c>
+      <c r="P3" s="5">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3">
+        <v>66.15384615384615</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="D4" s="3">
+        <v>32.30769230769231</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4.615384615384616</v>
+      </c>
+      <c r="F4" s="3">
+        <v>27.69230769230769</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0.1824967978052485</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0.140300171988524</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0.1191246136918766</v>
+      </c>
+      <c r="K4" s="4">
+        <v>71.80062794348493</v>
+      </c>
+      <c r="L4" s="4">
+        <v>73.2283600068828</v>
+      </c>
+      <c r="M4" s="5">
+        <v>65</v>
+      </c>
+      <c r="N4" s="5">
+        <v>688937.6592636108</v>
+      </c>
+      <c r="O4" s="4">
+        <v>57.1590192701909</v>
+      </c>
+      <c r="P4" s="5">
+        <v>12053</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="3">
+        <v>96.92307692307692</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.08800185297866568</v>
+      </c>
+      <c r="I5" s="4">
+        <v>0.05056214446562871</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.05273776795530023</v>
+      </c>
+      <c r="K5" s="4">
+        <v>86.04447933019379</v>
+      </c>
+      <c r="L5" s="4">
+        <v>90.50989502667515</v>
+      </c>
+      <c r="M5" s="5">
+        <v>65</v>
+      </c>
+      <c r="N5" s="5">
+        <v>686209.8686695099</v>
+      </c>
+      <c r="O5" s="4">
+        <v>158.844877006831</v>
+      </c>
+      <c r="P5" s="5">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="3">
+        <v>83.07692307692308</v>
+      </c>
+      <c r="C6" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="D6" s="3">
+        <v>13.84615384615385</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>13.84615384615385</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.2301311185651008</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.09039590441300981</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.09223972224799815</v>
+      </c>
+      <c r="K6" s="4">
+        <v>82.26059654631045</v>
+      </c>
+      <c r="L6" s="4">
+        <v>83.37842023748064</v>
+      </c>
+      <c r="M6" s="5">
+        <v>65</v>
+      </c>
+      <c r="N6" s="5">
+        <v>580285.0821018219</v>
+      </c>
+      <c r="O6" s="4">
+        <v>85.36114770547542</v>
+      </c>
+      <c r="P6" s="5">
+        <v>6798</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="3">
+        <v>95.38461538461539</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>4.615384615384616</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>4.615384615384616</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.08953064974289382</v>
+      </c>
+      <c r="I7" s="4">
+        <v>0.04339685755681948</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.04200988799148983</v>
+      </c>
+      <c r="K7" s="4">
+        <v>86.94139194139215</v>
+      </c>
+      <c r="L7" s="4">
+        <v>91.38926174496281</v>
+      </c>
+      <c r="M7" s="5">
+        <v>65</v>
+      </c>
+      <c r="N7" s="5">
+        <v>878003.0016899109</v>
+      </c>
+      <c r="O7" s="4">
+        <v>219.226717026195</v>
+      </c>
+      <c r="P7" s="5">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="3">
+        <v>93.84615384615384</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>6.153846153846154</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4">
+        <v>0.09713489805975625</v>
+      </c>
+      <c r="I8" s="4">
+        <v>0.06832074294549072</v>
+      </c>
+      <c r="J8" s="4">
+        <v>0.06774642072391528</v>
+      </c>
+      <c r="K8" s="4">
+        <v>86.00313971742565</v>
+      </c>
+      <c r="L8" s="4">
+        <v>89.93288590604195</v>
+      </c>
+      <c r="M8" s="5">
+        <v>65</v>
+      </c>
+      <c r="N8" s="5">
+        <v>65103.09767723083</v>
+      </c>
+      <c r="O8" s="4">
+        <v>15.44557477514373</v>
+      </c>
+      <c r="P8" s="5">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>87.69230769230769</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>12.30769230769231</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4">
+        <v>0.2559610977691249</v>
+      </c>
+      <c r="I9" s="4">
+        <v>0.1598046990807221</v>
+      </c>
+      <c r="J9" s="4">
+        <v>0.1487949404947748</v>
+      </c>
+      <c r="K9" s="4">
+        <v>80.10465724751438</v>
+      </c>
+      <c r="L9" s="4">
+        <v>81.88280846669913</v>
+      </c>
+      <c r="M9" s="5">
+        <v>65</v>
+      </c>
+      <c r="N9" s="5">
+        <v>245042.9632663727</v>
+      </c>
+      <c r="O9" s="4">
+        <v>29.20655104485968</v>
+      </c>
+      <c r="P9" s="5">
+        <v>8390</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="3">
+        <v>96.92307692307692</v>
+      </c>
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="4">
+        <v>0.09852245375034556</v>
+      </c>
+      <c r="I10" s="4">
+        <v>0.05388859849486697</v>
+      </c>
+      <c r="J10" s="4">
+        <v>0.05381798620574529</v>
+      </c>
+      <c r="K10" s="4">
+        <v>83.51334379905812</v>
+      </c>
+      <c r="L10" s="4">
+        <v>90.1302701772471</v>
+      </c>
+      <c r="M10" s="5">
+        <v>65</v>
+      </c>
+      <c r="N10" s="5">
+        <v>363694.3655014038</v>
+      </c>
+      <c r="O10" s="4">
+        <v>82.92165196110437</v>
+      </c>
+      <c r="P10" s="5">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="3">
+        <v>100</v>
+      </c>
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.1172116872151975</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.1172116872151975</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.1274611126448333</v>
+      </c>
+      <c r="K11" s="4">
+        <v>83.76452119309262</v>
+      </c>
+      <c r="L11" s="4">
+        <v>89.79401135776982</v>
+      </c>
+      <c r="M11" s="5">
+        <v>65</v>
+      </c>
+      <c r="N11" s="5">
+        <v>173753.8969516754</v>
+      </c>
+      <c r="O11" s="4">
+        <v>39.53444754304333</v>
+      </c>
+      <c r="P11" s="5">
+        <v>4395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="3">
+        <v>96.92307692307692</v>
+      </c>
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4">
+        <v>0.09310003361223429</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.05666924413893436</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.05992471971688394</v>
+      </c>
+      <c r="K12" s="4">
+        <v>80.27734170591329</v>
+      </c>
+      <c r="L12" s="4">
+        <v>88.12183789364718</v>
+      </c>
+      <c r="M12" s="5">
+        <v>65</v>
+      </c>
+      <c r="N12" s="5">
+        <v>91545.58324813843</v>
+      </c>
+      <c r="O12" s="4">
+        <v>19.90554104112599</v>
+      </c>
+      <c r="P12" s="5">
+        <v>4599</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="3">
+        <v>96.92307692307692</v>
+      </c>
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>3.076923076923077</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4">
+        <v>0.08368037793992791</v>
+      </c>
+      <c r="I13" s="4">
+        <v>0.05271377218722443</v>
+      </c>
+      <c r="J13" s="4">
+        <v>0.05328072151909037</v>
+      </c>
+      <c r="K13" s="4">
+        <v>85.81004709576142</v>
+      </c>
+      <c r="L13" s="4">
+        <v>90.65943899500645</v>
+      </c>
+      <c r="M13" s="5">
+        <v>65</v>
+      </c>
+      <c r="N13" s="5">
+        <v>296970.0620174408</v>
+      </c>
+      <c r="O13" s="4">
+        <v>74.14982821908634</v>
+      </c>
+      <c r="P13" s="5">
+        <v>4005</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="3">
+        <v>100</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0.02777887195116797</v>
+      </c>
+      <c r="I14" s="4">
+        <v>0.02777887195116797</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0.02805551968967614</v>
+      </c>
+      <c r="K14" s="4">
+        <v>97.06855049712192</v>
+      </c>
+      <c r="L14" s="4">
+        <v>98.26587506453281</v>
+      </c>
+      <c r="M14" s="5">
+        <v>65</v>
+      </c>
+      <c r="N14" s="5">
+        <v>1064915.188789368</v>
+      </c>
+      <c r="O14" s="4">
+        <v>338.0683139013866</v>
+      </c>
+      <c r="P14" s="5">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="3">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
+        <v>2</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.03554854357360267</v>
+      </c>
+      <c r="I15" s="4">
+        <v>0.03615837921564628</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0.03646355384706095</v>
+      </c>
+      <c r="K15" s="4">
+        <v>96.16462585034012</v>
+      </c>
+      <c r="L15" s="4">
+        <v>97.16689038031402</v>
+      </c>
+      <c r="M15" s="5">
+        <v>50</v>
+      </c>
+      <c r="N15" s="5">
+        <v>191186.9747638702</v>
+      </c>
+      <c r="O15" s="4">
+        <v>97.64401162608286</v>
+      </c>
+      <c r="P15" s="5">
+        <v>1958</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2221,13 +3671,13 @@
         <v>0</v>
       </c>
       <c r="L4" s="5">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M4" s="5">
         <v>0</v>
       </c>
       <c r="N4" s="5">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="25" customHeight="1">
@@ -2727,9 +4177,676 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" ht="25" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="25" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="5">
+        <v>58</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>6</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5">
+        <v>3</v>
+      </c>
+      <c r="M3" s="5">
+        <v>0</v>
+      </c>
+      <c r="N3" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="25" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="5">
+        <v>43</v>
+      </c>
+      <c r="C4" s="5">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>18</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>3</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>16</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="25" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="5">
+        <v>63</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="25" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5">
+        <v>54</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>9</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>6</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="25" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5">
+        <v>62</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>3</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="25" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="5">
+        <v>61</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>3</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="25" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="5">
+        <v>57</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>8</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5">
+        <v>4</v>
+      </c>
+      <c r="M9" s="5">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="25" customHeight="1">
+      <c r="A10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="5">
+        <v>63</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5">
+        <v>1</v>
+      </c>
+      <c r="M10" s="5">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="25" customHeight="1">
+      <c r="A11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="5">
+        <v>65</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5">
+        <v>0</v>
+      </c>
+      <c r="M11" s="5">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="25" customHeight="1">
+      <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="5">
+        <v>63</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5">
+        <v>1</v>
+      </c>
+      <c r="M12" s="5">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="25" customHeight="1">
+      <c r="A13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="5">
+        <v>63</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="25" customHeight="1">
+      <c r="A14" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="5">
+        <v>65</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="25" customHeight="1">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="5">
+        <v>49</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <v>0</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="K1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2740,9 +4857,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -2776,8 +4899,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2799,10 +4930,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
         <v>0.4312971836891777</v>
@@ -2840,9 +4989,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.4064439172041853</v>
+      </c>
+      <c r="O3" s="5">
+        <v>58</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1007170015231462</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05897705439066708</v>
+      </c>
+      <c r="R3" s="5">
+        <v>58</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2853,14 +5020,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -2871,9 +5039,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -2907,8 +5081,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -2930,10 +5112,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
         <v>0.294792421972782</v>
@@ -2971,9 +5171,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.1913034956444388</v>
+      </c>
+      <c r="O3" s="5">
+        <v>43</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.1824967978052485</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.140300171988524</v>
+      </c>
+      <c r="R3" s="5">
+        <v>43</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -2984,14 +5202,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3002,9 +5221,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -3038,8 +5263,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3061,10 +5294,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
         <v>0.3313296275329776</v>
@@ -3102,9 +5353,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2923341607286905</v>
+      </c>
+      <c r="O3" s="5">
+        <v>63</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08800185297866568</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.05056214446562871</v>
+      </c>
+      <c r="R3" s="5">
+        <v>63</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3115,14 +5384,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3133,9 +5403,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -3169,8 +5445,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3192,10 +5476,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
         <v>0.4423520654160082</v>
@@ -3233,9 +5535,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.3227152544156222</v>
+      </c>
+      <c r="O3" s="5">
+        <v>54</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.2301311185651008</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.09039590441300981</v>
+      </c>
+      <c r="R3" s="5">
+        <v>54</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3246,14 +5566,15 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -3264,9 +5585,15 @@
     <col min="11" max="11" width="20.7109375" customWidth="1"/>
     <col min="12" max="12" width="25.7109375" customWidth="1"/>
     <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="22.7109375" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" customWidth="1"/>
+    <col min="18" max="18" width="20.7109375" customWidth="1"/>
+    <col min="19" max="19" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
+    <row r="1" spans="1:19" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -3300,8 +5627,16 @@
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
+      <c r="N1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="25" customHeight="1">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3323,10 +5658,28 @@
       <c r="M2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
+      <c r="N2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B3" s="4">
         <v>0.2800297065069361</v>
@@ -3364,9 +5717,27 @@
       <c r="M3" s="5">
         <v>0</v>
       </c>
+      <c r="N3" s="4">
+        <v>-0.2392546644156438</v>
+      </c>
+      <c r="O3" s="5">
+        <v>62</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0.08953064974289382</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0.04339685755681948</v>
+      </c>
+      <c r="R3" s="5">
+        <v>62</v>
+      </c>
+      <c r="S3" s="5">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
@@ -3377,268 +5748,7 @@
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.3185467934058848</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.285872539110592</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.2824052655040622</v>
-      </c>
-      <c r="E3" s="4">
-        <v>86.00313971742565</v>
-      </c>
-      <c r="F3" s="4">
-        <v>89.93288590604195</v>
-      </c>
-      <c r="G3" s="5">
-        <v>65</v>
-      </c>
-      <c r="H3" s="5">
-        <v>61</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>4</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>4</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="4" width="18.7109375" customWidth="1"/>
-    <col min="5" max="8" width="15.7109375" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" customWidth="1"/>
-    <col min="12" max="12" width="25.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:13" ht="25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="25" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.4458304534395351</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.3637836354814282</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.3383042683554007</v>
-      </c>
-      <c r="E3" s="4">
-        <v>80.10465724751438</v>
-      </c>
-      <c r="F3" s="4">
-        <v>81.88280846669913</v>
-      </c>
-      <c r="G3" s="5">
-        <v>65</v>
-      </c>
-      <c r="H3" s="5">
-        <v>57</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="5">
-        <v>8</v>
-      </c>
-      <c r="K3" s="5">
-        <v>0</v>
-      </c>
-      <c r="L3" s="5">
-        <v>8</v>
-      </c>
-      <c r="M3" s="5">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/public/downloads/TangModeling2020.xlsx
+++ b/public/downloads/TangModeling2020.xlsx
@@ -1443,16 +1443,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.285872539110592</v>
+        <v>-0.280933179617108</v>
       </c>
       <c r="O3" s="5">
         <v>61</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09713489805975625</v>
+        <v>0.09701824009932727</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.06832074294549072</v>
+        <v>0.06803448906983739</v>
       </c>
       <c r="R3" s="5">
         <v>61</v>
@@ -1625,16 +1625,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3573543718682087</v>
+        <v>-0.3472531669467571</v>
       </c>
       <c r="O3" s="5">
         <v>57</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2559610977691249</v>
+        <v>0.2557438477926413</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1598046990807221</v>
+        <v>0.159202529636611</v>
       </c>
       <c r="R3" s="5">
         <v>57</v>
@@ -1807,16 +1807,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1893666925516583</v>
+        <v>-0.1890725171531202</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09852245375034556</v>
+        <v>0.0985174538624265</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05388859849486697</v>
+        <v>0.0538834398803473</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -1989,16 +1989,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2975776994144186</v>
+        <v>-0.2928518723419984</v>
       </c>
       <c r="O3" s="5">
         <v>65</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1172116872151975</v>
+        <v>0.1170017067603812</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.1172116872151975</v>
+        <v>0.1170017067603812</v>
       </c>
       <c r="R3" s="5">
         <v>65</v>
@@ -2171,16 +2171,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2897454035183828</v>
+        <v>-0.295783043562551</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>0.09310003361223429</v>
+        <v>0.09268310612533241</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05666924413893436</v>
+        <v>0.05623908085879752</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -2353,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4588009637968969</v>
+        <v>-0.4485816774249543</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08368037793992791</v>
+        <v>0.0831020426786451</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05271377218722443</v>
+        <v>0.05211707707637707</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -2535,16 +2535,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.08938248716024445</v>
+        <v>-0.08852608577583965</v>
       </c>
       <c r="O3" s="5">
         <v>65</v>
       </c>
       <c r="P3" s="4">
-        <v>0.02777887195116797</v>
+        <v>0.02775071179113562</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.02777887195116797</v>
+        <v>0.02775071179113562</v>
       </c>
       <c r="R3" s="5">
         <v>65</v>
@@ -2717,16 +2717,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.0976706311271209</v>
+        <v>-0.08860296706555459</v>
       </c>
       <c r="O3" s="5">
         <v>49</v>
       </c>
       <c r="P3" s="4">
-        <v>0.03554854357360267</v>
+        <v>0.034632109727529</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.03615837921564628</v>
+        <v>0.03526947794751734</v>
       </c>
       <c r="R3" s="5">
         <v>49</v>
@@ -2863,13 +2863,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="4">
-        <v>0.1007170015231462</v>
+        <v>0.09962661043156494</v>
       </c>
       <c r="I3" s="4">
-        <v>0.05897705439066708</v>
+        <v>0.05755674771014661</v>
       </c>
       <c r="J3" s="4">
-        <v>0.06088286313725737</v>
+        <v>0.06002763999802902</v>
       </c>
       <c r="K3" s="4">
         <v>85.24803767660921</v>
@@ -2913,13 +2913,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="4">
-        <v>0.1824967978052485</v>
+        <v>0.1837304440773621</v>
       </c>
       <c r="I4" s="4">
-        <v>0.140300171988524</v>
+        <v>0.140175851046373</v>
       </c>
       <c r="J4" s="4">
-        <v>0.1191246136918766</v>
+        <v>0.1193882172677639</v>
       </c>
       <c r="K4" s="4">
         <v>71.80062794348493</v>
@@ -2963,13 +2963,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="4">
-        <v>0.08800185297866568</v>
+        <v>0.08725244095011686</v>
       </c>
       <c r="I5" s="4">
-        <v>0.05056214446562871</v>
+        <v>0.05005321085465968</v>
       </c>
       <c r="J5" s="4">
-        <v>0.05273776795530023</v>
+        <v>0.05305020850657736</v>
       </c>
       <c r="K5" s="4">
         <v>86.04447933019379</v>
@@ -3013,13 +3013,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="4">
-        <v>0.2301311185651008</v>
+        <v>0.2291626589484132</v>
       </c>
       <c r="I6" s="4">
-        <v>0.09039590441300981</v>
+        <v>0.08887958653536367</v>
       </c>
       <c r="J6" s="4">
-        <v>0.09223972224799815</v>
+        <v>0.09022527918719929</v>
       </c>
       <c r="K6" s="4">
         <v>82.26059654631045</v>
@@ -3063,13 +3063,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="4">
-        <v>0.08953064974289382</v>
+        <v>0.08773450537230998</v>
       </c>
       <c r="I7" s="4">
-        <v>0.04339685755681948</v>
+        <v>0.04121092706942187</v>
       </c>
       <c r="J7" s="4">
-        <v>0.04200988799148983</v>
+        <v>0.04014776169653767</v>
       </c>
       <c r="K7" s="4">
         <v>86.94139194139215</v>
@@ -3113,13 +3113,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="4">
-        <v>0.09713489805975625</v>
+        <v>0.09701824009932727</v>
       </c>
       <c r="I8" s="4">
-        <v>0.06832074294549072</v>
+        <v>0.06803448906983739</v>
       </c>
       <c r="J8" s="4">
-        <v>0.06774642072391528</v>
+        <v>0.06764141735638139</v>
       </c>
       <c r="K8" s="4">
         <v>86.00313971742565</v>
@@ -3163,13 +3163,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="4">
-        <v>0.2559610977691249</v>
+        <v>0.2557438477926413</v>
       </c>
       <c r="I9" s="4">
-        <v>0.1598046990807221</v>
+        <v>0.159202529636611</v>
       </c>
       <c r="J9" s="4">
-        <v>0.1487949404947748</v>
+        <v>0.147921255447951</v>
       </c>
       <c r="K9" s="4">
         <v>80.10465724751438</v>
@@ -3213,13 +3213,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="4">
-        <v>0.09852245375034556</v>
+        <v>0.0985174538624265</v>
       </c>
       <c r="I10" s="4">
-        <v>0.05388859849486697</v>
+        <v>0.0538834398803473</v>
       </c>
       <c r="J10" s="4">
-        <v>0.05381798620574529</v>
+        <v>0.05384061508255591</v>
       </c>
       <c r="K10" s="4">
         <v>83.51334379905812</v>
@@ -3263,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="4">
-        <v>0.1172116872151975</v>
+        <v>0.1170017067603812</v>
       </c>
       <c r="I11" s="4">
-        <v>0.1172116872151975</v>
+        <v>0.1170017067603812</v>
       </c>
       <c r="J11" s="4">
-        <v>0.1274611126448333</v>
+        <v>0.1272429975491832</v>
       </c>
       <c r="K11" s="4">
         <v>83.76452119309262</v>
@@ -3313,13 +3313,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="4">
-        <v>0.09310003361223429</v>
+        <v>0.09268310612533241</v>
       </c>
       <c r="I12" s="4">
-        <v>0.05666924413893436</v>
+        <v>0.05623908085879752</v>
       </c>
       <c r="J12" s="4">
-        <v>0.05992471971688394</v>
+        <v>0.05881029052565841</v>
       </c>
       <c r="K12" s="4">
         <v>80.27734170591329</v>
@@ -3363,13 +3363,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="4">
-        <v>0.08368037793992791</v>
+        <v>0.0831020426786451</v>
       </c>
       <c r="I13" s="4">
-        <v>0.05271377218722443</v>
+        <v>0.05211707707637707</v>
       </c>
       <c r="J13" s="4">
-        <v>0.05328072151909037</v>
+        <v>0.05184831805370498</v>
       </c>
       <c r="K13" s="4">
         <v>85.81004709576142</v>
@@ -3413,13 +3413,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="4">
-        <v>0.02777887195116797</v>
+        <v>0.02775071179113562</v>
       </c>
       <c r="I14" s="4">
-        <v>0.02777887195116797</v>
+        <v>0.02775071179113562</v>
       </c>
       <c r="J14" s="4">
-        <v>0.02805551968967614</v>
+        <v>0.02806869509559006</v>
       </c>
       <c r="K14" s="4">
         <v>97.06855049712192</v>
@@ -3463,13 +3463,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="4">
-        <v>0.03554854357360267</v>
+        <v>0.034632109727529</v>
       </c>
       <c r="I15" s="4">
-        <v>0.03615837921564628</v>
+        <v>0.03526947794751734</v>
       </c>
       <c r="J15" s="4">
-        <v>0.03646355384706095</v>
+        <v>0.03521110555708726</v>
       </c>
       <c r="K15" s="4">
         <v>96.16462585034012</v>
@@ -4990,16 +4990,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.4064439172041853</v>
+        <v>-0.3949415506867808</v>
       </c>
       <c r="O3" s="5">
         <v>58</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1007170015231462</v>
+        <v>0.09962661043156494</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05897705439066708</v>
+        <v>0.05755674771014661</v>
       </c>
       <c r="R3" s="5">
         <v>58</v>
@@ -5172,16 +5172,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.1913034956444388</v>
+        <v>-0.1859576951319468</v>
       </c>
       <c r="O3" s="5">
         <v>43</v>
       </c>
       <c r="P3" s="4">
-        <v>0.1824967978052485</v>
+        <v>0.1837304440773621</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.140300171988524</v>
+        <v>0.140175851046373</v>
       </c>
       <c r="R3" s="5">
         <v>43</v>
@@ -5354,16 +5354,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2923341607286905</v>
+        <v>-0.300658642911003</v>
       </c>
       <c r="O3" s="5">
         <v>63</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08800185297866568</v>
+        <v>0.08725244095011686</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.05056214446562871</v>
+        <v>0.05005321085465968</v>
       </c>
       <c r="R3" s="5">
         <v>63</v>
@@ -5536,16 +5536,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.3227152544156222</v>
+        <v>-0.3037839641074243</v>
       </c>
       <c r="O3" s="5">
         <v>54</v>
       </c>
       <c r="P3" s="4">
-        <v>0.2301311185651008</v>
+        <v>0.2291626589484132</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.09039590441300981</v>
+        <v>0.08887958653536367</v>
       </c>
       <c r="R3" s="5">
         <v>54</v>
@@ -5718,16 +5718,16 @@
         <v>0</v>
       </c>
       <c r="N3" s="4">
-        <v>-0.2392546644156438</v>
+        <v>-0.2204763582849409</v>
       </c>
       <c r="O3" s="5">
         <v>62</v>
       </c>
       <c r="P3" s="4">
-        <v>0.08953064974289382</v>
+        <v>0.08773450537230998</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.04339685755681948</v>
+        <v>0.04121092706942187</v>
       </c>
       <c r="R3" s="5">
         <v>62</v>
